--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487470_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487470_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3347</v>
+        <v>4.452</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9569</v>
+        <v>5.6732</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6222</v>
+        <v>-1.2212</v>
       </c>
       <c r="G2" t="n">
         <v>3.3894</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3301</v>
+        <v>-0.2128</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5156</v>
+        <v>-0.7993</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1856</v>
+        <v>0.5865</v>
       </c>
       <c r="V2" t="n">
         <v>0.8837</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8821</v>
+        <v>1.4586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2917</v>
+        <v>-1.3457</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5904</v>
+        <v>2.8043</v>
       </c>
       <c r="G3" t="n">
         <v>1.5028</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4381</v>
+        <v>1.0145</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4607</v>
+        <v>0.8234</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0227</v>
+        <v>0.1911</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2754</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8265</v>
+        <v>1.1151</v>
       </c>
       <c r="E4" t="n">
-        <v>1.774</v>
+        <v>2.4904</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9476</v>
+        <v>-1.3753</v>
       </c>
       <c r="G4" t="n">
         <v>0.3983</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1724</v>
+        <v>0.4611</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2186</v>
+        <v>-0.5023</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3911</v>
+        <v>0.9634</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7235</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3374</v>
+        <v>-0.2061</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0299</v>
+        <v>-0.2283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3075</v>
+        <v>0.0222</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3793</v>
+        <v>1.1547</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8391</v>
+        <v>1.6901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4598</v>
+        <v>-0.5354</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0398</v>
+        <v>0.6652</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4287</v>
+        <v>1.3474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.611</v>
+        <v>-0.6822</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6604</v>
+        <v>0.4895</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4104</v>
+        <v>0.3427</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0708</v>
+        <v>0.1468</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7834</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7415</v>
+        <v>-0.1822</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9487</v>
+        <v>-0.2276</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2072</v>
+        <v>0.0454</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3795</v>
+        <v>-0.4057</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5353</v>
+        <v>-0.6864</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1559</v>
+        <v>0.2807</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1547</v>
+        <v>0.3793</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6901</v>
+        <v>0.8391</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5354</v>
+        <v>-0.4598</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6652</v>
+        <v>1.0398</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3474</v>
+        <v>0.4287</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6822</v>
+        <v>0.611</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4895</v>
+        <v>-0.6604</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3427</v>
+        <v>0.4104</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1468</v>
+        <v>-1.0708</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3555</v>
+        <v>-0.0016</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5346</v>
+        <v>0.2323</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1791</v>
+        <v>-0.2339</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>M. FERNANDEZ ZAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5374</v>
+        <v>-1.1045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7092000000000001</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2466</v>
+        <v>-0.2119</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.902</v>
+        <v>0.21</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.2902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1112</v>
+        <v>0.5002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7543</v>
+        <v>1.4818</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5939</v>
+        <v>0.1837</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3482</v>
+        <v>1.2981</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6563</v>
+        <v>-1.2718</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1969</v>
+        <v>-0.4739</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4594</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5432</v>
+        <v>-0.6486</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3835</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1598</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1578</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5507</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RUANO MARTINEZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9137</v>
+        <v>-1.5035</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.907</v>
+        <v>0.1975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9933</v>
+        <v>-1.701</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7358</v>
+        <v>-0.902</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.246</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4898</v>
+        <v>-0.1112</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2743</v>
+        <v>0.7543</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3148</v>
+        <v>-0.5939</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0404</v>
+        <v>1.3482</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4615</v>
+        <v>-1.6563</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0687</v>
+        <v>-0.1969</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5302</v>
+        <v>-1.4594</v>
       </c>
       <c r="P8" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9585</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8014</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3258</v>
+        <v>-0.1282</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4756</v>
+        <v>0.7053</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ ZAS</t>
+          <t>M. RUANO MARTINEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.287</v>
+        <v>-1.5369</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9949</v>
+        <v>-2.3164</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2921</v>
+        <v>0.7795</v>
       </c>
       <c r="G9" t="n">
-        <v>0.21</v>
+        <v>-0.7358</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2902</v>
+        <v>-0.246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5002</v>
+        <v>-0.4898</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4818</v>
+        <v>-0.2743</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1837</v>
+        <v>-0.3148</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2981</v>
+        <v>0.0404</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2718</v>
+        <v>-0.4615</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4739</v>
+        <v>0.0687</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5302</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8310999999999999</v>
+        <v>0.1782</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8316</v>
+        <v>-0.0835</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0005</v>
+        <v>0.2617</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1616</v>
+        <v>-2.7622</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5963000000000001</v>
+        <v>-0.7842</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7578</v>
+        <v>-1.978</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3877</v>
+        <v>0.0948</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8456</v>
+        <v>-0.8143</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2332</v>
+        <v>0.9092</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3685</v>
+        <v>-0.2154</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0007</v>
+        <v>-1.3663</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6322</v>
+        <v>1.1509</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7562</v>
+        <v>0.3103</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1551</v>
+        <v>0.552</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.601</v>
+        <v>-0.2417</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1751</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8487</v>
+        <v>-0.1485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7722</v>
+        <v>-0.4352</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0765</v>
+        <v>0.2867</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1003</v>
+        <v>-2.7086</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1003</v>
+        <v>-4.5335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4714</v>
+        <v>-2.8767</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0123</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4591</v>
+        <v>-3.6776</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0948</v>
+        <v>-1.3877</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8143</v>
+        <v>0.8456</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9092</v>
+        <v>-2.2332</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2154</v>
+        <v>1.3685</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3663</v>
+        <v>2.0007</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1509</v>
+        <v>-0.6322</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3103</v>
+        <v>-2.7562</v>
       </c>
       <c r="N11" t="n">
-        <v>0.552</v>
+        <v>-1.1551</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2417</v>
+        <v>-1.601</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8577</v>
+        <v>-0.5639</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6633</v>
+        <v>-0.5676</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1944</v>
+        <v>0.0037</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7086</v>
+        <v>-2.1003</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.5335</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3699</v>
+        <v>-3.369900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.908500000000001</v>
+        <v>2.9084</v>
       </c>
       <c r="F12" t="n">
         <v>-6.2783</v>
@@ -1366,7 +1366,7 @@
         <v>12.9844</v>
       </c>
       <c r="K12" t="n">
-        <v>7.103699999999999</v>
+        <v>7.103700000000001</v>
       </c>
       <c r="L12" t="n">
         <v>5.8806</v>
@@ -1378,7 +1378,7 @@
         <v>-0.2968999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.583499999999999</v>
+        <v>-8.583500000000001</v>
       </c>
       <c r="P12" t="n">
         <v>1.9584</v>
@@ -1390,13 +1390,13 @@
         <v>14.6886</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4735</v>
+        <v>0.4732999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4172</v>
+        <v>-2.4173</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8909</v>
+        <v>2.8906</v>
       </c>
       <c r="V12" t="n">
         <v>-9.9056</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.018800000000001</v>
+        <v>6.0423</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0189</v>
+        <v>5.7908</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999</v>
+        <v>0.2514</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1287</v>
@@ -1468,13 +1468,13 @@
         <v>2.1543</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5529</v>
+        <v>0.5764</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8280999999999999</v>
+        <v>-0.3999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7248</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>7.3572</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5097</v>
+        <v>4.1596</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5614</v>
+        <v>3.9707</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0517</v>
+        <v>0.1889</v>
       </c>
       <c r="G14" t="n">
         <v>6.0747</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6054</v>
+        <v>0.0446</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6775</v>
+        <v>-0.2682</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0722</v>
+        <v>0.3127</v>
       </c>
       <c r="V14" t="n">
         <v>0.3905</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0349</v>
+        <v>4.1125</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5577</v>
+        <v>3.9671</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5228</v>
+        <v>0.1454</v>
       </c>
       <c r="G15" t="n">
         <v>1.4521</v>
@@ -1624,13 +1624,13 @@
         <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9288</v>
+        <v>-0.8512</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8734</v>
+        <v>-0.464</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0554</v>
+        <v>-0.3871</v>
       </c>
       <c r="V15" t="n">
         <v>3.7074</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.155</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1608</v>
+        <v>-0.9741</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0058</v>
+        <v>1.0475</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7292</v>
+        <v>-0.1827</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4311</v>
+        <v>-0.1827</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2981</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2532</v>
+        <v>0.0204</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3437</v>
+        <v>0.0204</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0905</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.476</v>
+        <v>-0.2031</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0874</v>
+        <v>-0.2031</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3886</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7886</v>
+        <v>-0.0181</v>
       </c>
       <c r="T16" t="n">
-        <v>0.414</v>
+        <v>-0.0153</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3746</v>
+        <v>-0.0028</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2754</v>
+        <v>0.6659</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.1454</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1125</v>
+        <v>-0.7188</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.212</v>
+        <v>0.5733</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8822</v>
+        <v>-0.6708</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1195</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7627</v>
+        <v>-0.01</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0688</v>
+        <v>-0.5406</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5085</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4397</v>
+        <v>0.1212</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.951</v>
+        <v>-0.1302</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.628</v>
+        <v>0.001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3229</v>
+        <v>-0.1313</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6985</v>
+        <v>-0.0622</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3305</v>
+        <v>-0.1782</v>
       </c>
       <c r="U17" t="n">
-        <v>1.368</v>
+        <v>0.116</v>
       </c>
       <c r="V17" t="n">
-        <v>2.651</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.651</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>R. CACHON VILLAMEDIANA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1187</v>
+        <v>-0.2258</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7188</v>
+        <v>-1.3904</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6001</v>
+        <v>1.1646</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6708</v>
+        <v>-0.2289</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.7339</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01</v>
+        <v>0.505</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5406</v>
+        <v>0.7023</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6006</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1212</v>
+        <v>1.3029</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1302</v>
+        <v>-0.9312</v>
       </c>
       <c r="N18" t="n">
-        <v>0.001</v>
+        <v>-0.1333</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1313</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0355</v>
+        <v>0.0815</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1782</v>
+        <v>-0.4476</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1427</v>
+        <v>0.529</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2115</v>
+        <v>-0.2765</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1788</v>
+        <v>-0.3509</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9673</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1827</v>
+        <v>-1.7292</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1827</v>
+        <v>-1.4311</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.2981</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0204</v>
+        <v>-0.2532</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0204</v>
+        <v>-0.3437</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0905</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2031</v>
+        <v>-1.476</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2031</v>
+        <v>-1.0874</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.3886</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3029</v>
+        <v>0.3571</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.22</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.083</v>
+        <v>0.4548</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. CACHON VILLAMEDIANA</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4793</v>
+        <v>-1.3107</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6974</v>
+        <v>-0.2968</v>
       </c>
       <c r="F20" t="n">
-        <v>1.218</v>
+        <v>-1.0139</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2289</v>
+        <v>-2.8822</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7339</v>
+        <v>-1.1195</v>
       </c>
       <c r="I20" t="n">
-        <v>0.505</v>
+        <v>-1.7627</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7023</v>
+        <v>0.0688</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6006</v>
+        <v>0.5085</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3029</v>
+        <v>-0.4397</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9312</v>
+        <v>-2.951</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1333</v>
+        <v>-1.628</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.3229</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1721</v>
+        <v>0.4873</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7546</v>
+        <v>-0.0788</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5825</v>
+        <v>0.5661</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6659</v>
+        <v>2.651</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6659</v>
+        <v>2.651</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7373</v>
+        <v>-2.856</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7705</v>
+        <v>-2.1565</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9668</v>
+        <v>-0.6995</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9901</v>
@@ -2092,13 +2092,13 @@
         <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6262</v>
+        <v>-0.7449</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0339</v>
+        <v>-0.4199</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3249</v>
       </c>
       <c r="V21" t="n">
         <v>-1.492</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7022</v>
+        <v>-6.2035</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7676</v>
+        <v>-1.5629</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9346</v>
+        <v>-4.6406</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8181</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8426</v>
+        <v>-0.3439</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7258</v>
+        <v>-0.5211</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1169</v>
+        <v>0.1772</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4332</v>
@@ -2203,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.3699</v>
+        <v>3.369900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>6.278200000000002</v>
+        <v>6.278200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9084</v>
+        <v>-2.9085</v>
       </c>
       <c r="G23" t="n">
         <v>-4.103899999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.806699999999999</v>
+        <v>-6.806700000000001</v>
       </c>
       <c r="I23" t="n">
         <v>2.703</v>
       </c>
       <c r="J23" t="n">
-        <v>8.880500000000001</v>
+        <v>8.880499999999998</v>
       </c>
       <c r="K23" t="n">
         <v>0.2967999999999997</v>
       </c>
       <c r="L23" t="n">
-        <v>8.583599999999999</v>
+        <v>8.583600000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-12.9842</v>
@@ -2239,7 +2239,7 @@
         <v>-5.8806</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9586</v>
+        <v>-1.958600000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.6885</v>
@@ -2248,10 +2248,10 @@
         <v>12.7299</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4735000000000003</v>
+        <v>-0.4733999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.8908</v>
+        <v>-2.8906</v>
       </c>
       <c r="U23" t="n">
         <v>2.4173</v>
